--- a/태화라이온스 회비납부 안내.xlsx
+++ b/태화라이온스 회비납부 안내.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\이재원\클로드코딩\태화라이온스\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{798A01CC-A93F-4604-9AA9-D730FCE5C5CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26BB3031-B069-498E-B5B3-654EF1941C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{99096A5B-9985-413D-8469-2B24DEA33801}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>안녕하십니까 존경하는 라이온스 회원여러분</t>
   </si>
@@ -68,17 +68,7 @@
     <t>7. 지구연차대회 30,000원</t>
   </si>
   <si>
-    <t>8. 경조사비  현재 10000원</t>
-  </si>
-  <si>
-    <t>합계 1,040,000원(전회원 동일/경조사시 당사자1만원 제외) 입니다.</t>
-  </si>
-  <si>
     <t>내용 참고 하셔서 회비 납부 부탁드립니다.</t>
-  </si>
-  <si>
-    <t>카카오뱅크 3333-37-8510096 이재원 입니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>태화라이온스클럽 회비납부 계좌번호 알려드립니다.</t>
@@ -86,6 +76,14 @@
   </si>
   <si>
     <t>2026-2027 재무 이재원 올림.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>합계 1,030,000원(전회원 동일/경조사시 당사자1만원 제외) 입니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수협 2010-0951-6660 태화라이온스클럽 입니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -470,7 +468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDDEE97E-2680-4A54-B531-424CB147B5C1}">
-  <dimension ref="A2:A31"/>
+  <dimension ref="A2:A30"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
@@ -523,19 +521,19 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
@@ -543,14 +541,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>15</v>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
